--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.90254</v>
+        <v>18.00995</v>
       </c>
       <c r="D2" t="n">
-        <v>17.24601</v>
+        <v>17.20965</v>
       </c>
       <c r="E2" t="n">
-        <v>17.39602</v>
+        <v>17.71703</v>
       </c>
       <c r="F2" t="n">
-        <v>44.66084</v>
+        <v>45.21378</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05372</v>
+        <v>0.05316</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88766</v>
+        <v>1.90945</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.65487</v>
+        <v>17.70819</v>
       </c>
       <c r="D3" t="n">
-        <v>17.95293</v>
+        <v>17.32573</v>
       </c>
       <c r="E3" t="n">
-        <v>17.73631</v>
+        <v>17.52001</v>
       </c>
       <c r="F3" t="n">
-        <v>44.59238</v>
+        <v>44.17604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05278</v>
+        <v>0.05283</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90861</v>
+        <v>1.94899</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.33681</v>
+        <v>17.47864</v>
       </c>
       <c r="D4" t="n">
-        <v>17.42616</v>
+        <v>17.14179</v>
       </c>
       <c r="E4" t="n">
-        <v>17.53054</v>
+        <v>17.36194</v>
       </c>
       <c r="F4" t="n">
-        <v>44.09485</v>
+        <v>44.71134</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0531</v>
+        <v>0.05269</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93334</v>
+        <v>1.91105</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.90497</v>
+        <v>17.6801</v>
       </c>
       <c r="D5" t="n">
-        <v>17.68979</v>
+        <v>17.13269</v>
       </c>
       <c r="E5" t="n">
-        <v>17.4599</v>
+        <v>17.54935</v>
       </c>
       <c r="F5" t="n">
-        <v>44.28251</v>
+        <v>45.11977</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05283</v>
+        <v>0.05361</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9095</v>
+        <v>1.8929</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.52324</v>
+        <v>17.44295</v>
       </c>
       <c r="D6" t="n">
-        <v>17.39697</v>
+        <v>17.08907</v>
       </c>
       <c r="E6" t="n">
-        <v>17.34886</v>
+        <v>17.25037</v>
       </c>
       <c r="F6" t="n">
-        <v>44.44654</v>
+        <v>44.77992</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05368</v>
+        <v>0.05204</v>
       </c>
       <c r="H6" t="n">
-        <v>1.87384</v>
+        <v>1.90581</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.81174</v>
+        <v>17.60431</v>
       </c>
       <c r="D7" t="n">
-        <v>17.30295</v>
+        <v>17.16514</v>
       </c>
       <c r="E7" t="n">
-        <v>17.5158</v>
+        <v>17.2425</v>
       </c>
       <c r="F7" t="n">
-        <v>45.04906</v>
+        <v>43.23884</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05194</v>
+        <v>0.05213</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89155</v>
+        <v>1.90957</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.00286</v>
+        <v>17.60116</v>
       </c>
       <c r="D8" t="n">
-        <v>17.60452</v>
+        <v>17.44252</v>
       </c>
       <c r="E8" t="n">
-        <v>17.50801</v>
+        <v>17.45326</v>
       </c>
       <c r="F8" t="n">
-        <v>44.79069</v>
+        <v>44.55181</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05386</v>
+        <v>0.05334</v>
       </c>
       <c r="H8" t="n">
-        <v>1.90422</v>
+        <v>1.94822</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.7839</v>
+        <v>17.66408</v>
       </c>
       <c r="D9" t="n">
-        <v>17.61933</v>
+        <v>17.44545</v>
       </c>
       <c r="E9" t="n">
-        <v>17.2664</v>
+        <v>17.55893</v>
       </c>
       <c r="F9" t="n">
-        <v>44.09855</v>
+        <v>43.77459</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05388</v>
+        <v>0.05363</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92055</v>
+        <v>1.92924</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.76907</v>
+        <v>17.47933</v>
       </c>
       <c r="D10" t="n">
-        <v>17.17463</v>
+        <v>16.99936</v>
       </c>
       <c r="E10" t="n">
-        <v>17.60619</v>
+        <v>17.40497</v>
       </c>
       <c r="F10" t="n">
-        <v>44.78015</v>
+        <v>44.09505</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05337</v>
+        <v>0.0539</v>
       </c>
       <c r="H10" t="n">
-        <v>1.92833</v>
+        <v>1.8973</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.88854</v>
+        <v>17.78821</v>
       </c>
       <c r="D12" t="n">
-        <v>17.44379</v>
+        <v>17.18104</v>
       </c>
       <c r="E12" t="n">
-        <v>17.58824</v>
+        <v>17.56339</v>
       </c>
       <c r="F12" t="n">
-        <v>43.97757</v>
+        <v>44.62283</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05372</v>
+        <v>0.05323</v>
       </c>
       <c r="H12" t="n">
-        <v>1.86078</v>
+        <v>1.88804</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.71726</v>
+        <v>17.41963</v>
       </c>
       <c r="D13" t="n">
-        <v>17.04873</v>
+        <v>17.2455</v>
       </c>
       <c r="E13" t="n">
-        <v>17.72075</v>
+        <v>17.32772</v>
       </c>
       <c r="F13" t="n">
-        <v>44.42151</v>
+        <v>44.61411</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05297</v>
+        <v>0.05393</v>
       </c>
       <c r="H13" t="n">
-        <v>1.90078</v>
+        <v>1.90853</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.48814</v>
+        <v>17.90702</v>
       </c>
       <c r="D14" t="n">
-        <v>17.22459</v>
+        <v>17.4608</v>
       </c>
       <c r="E14" t="n">
-        <v>17.33342</v>
+        <v>17.52494</v>
       </c>
       <c r="F14" t="n">
-        <v>44.0631</v>
+        <v>44.73343</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05356</v>
+        <v>0.05327</v>
       </c>
       <c r="H14" t="n">
-        <v>1.92928</v>
+        <v>1.90679</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.67046</v>
+        <v>17.50265</v>
       </c>
       <c r="D15" t="n">
-        <v>16.71331</v>
+        <v>17.4049</v>
       </c>
       <c r="E15" t="n">
-        <v>17.47853</v>
+        <v>17.41126</v>
       </c>
       <c r="F15" t="n">
-        <v>44.07956</v>
+        <v>44.33086</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05342</v>
+        <v>0.0512</v>
       </c>
       <c r="H15" t="n">
-        <v>1.89401</v>
+        <v>1.92331</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.75257</v>
+        <v>17.74295</v>
       </c>
       <c r="D16" t="n">
-        <v>17.16692</v>
+        <v>17.38768</v>
       </c>
       <c r="E16" t="n">
-        <v>17.52119</v>
+        <v>17.55037</v>
       </c>
       <c r="F16" t="n">
-        <v>44.80942</v>
+        <v>44.10967</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0535</v>
+        <v>0.05393</v>
       </c>
       <c r="H16" t="n">
-        <v>1.87727</v>
+        <v>1.90068</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.34778</v>
+        <v>17.85582</v>
       </c>
       <c r="D17" t="n">
-        <v>17.25777</v>
+        <v>17.26818</v>
       </c>
       <c r="E17" t="n">
-        <v>17.70156</v>
+        <v>17.52933</v>
       </c>
       <c r="F17" t="n">
-        <v>44.99915</v>
+        <v>45.20277</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05273</v>
+        <v>0.05154</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89482</v>
+        <v>1.90245</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18.04745</v>
+        <v>17.55904</v>
       </c>
       <c r="D18" t="n">
-        <v>17.43735</v>
+        <v>17.25448</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7176</v>
+        <v>17.4339</v>
       </c>
       <c r="F18" t="n">
-        <v>45.74002</v>
+        <v>43.70495</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05366</v>
+        <v>0.05205</v>
       </c>
       <c r="H18" t="n">
-        <v>1.88156</v>
+        <v>1.92828</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.38799</v>
+        <v>17.84138</v>
       </c>
       <c r="D19" t="n">
-        <v>17.88281</v>
+        <v>17.67938</v>
       </c>
       <c r="E19" t="n">
-        <v>17.03374</v>
+        <v>17.77962</v>
       </c>
       <c r="F19" t="n">
-        <v>45.17749</v>
+        <v>44.17934</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05285</v>
+        <v>0.0532</v>
       </c>
       <c r="H19" t="n">
-        <v>1.87326</v>
+        <v>1.88877</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.63275</v>
+        <v>17.8126</v>
       </c>
       <c r="D20" t="n">
-        <v>17.45678</v>
+        <v>17.53892</v>
       </c>
       <c r="E20" t="n">
-        <v>17.26418</v>
+        <v>17.73484</v>
       </c>
       <c r="F20" t="n">
-        <v>46.38759</v>
+        <v>43.96503</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05344</v>
+        <v>0.05283</v>
       </c>
       <c r="H20" t="n">
-        <v>1.94977</v>
+        <v>1.86844</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.63295</v>
+        <v>16.62658</v>
       </c>
       <c r="D22" t="n">
-        <v>16.21672</v>
+        <v>16.38764</v>
       </c>
       <c r="E22" t="n">
-        <v>16.27577</v>
+        <v>16.57225</v>
       </c>
       <c r="F22" t="n">
-        <v>261.11617</v>
+        <v>265.96625</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.48424</v>
+        <v>16.47793</v>
       </c>
       <c r="D23" t="n">
-        <v>16.07705</v>
+        <v>16.29094</v>
       </c>
       <c r="E23" t="n">
-        <v>16.10757</v>
+        <v>16.37791</v>
       </c>
       <c r="F23" t="n">
-        <v>264.2515</v>
+        <v>265.75059</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.48025</v>
+        <v>16.66866</v>
       </c>
       <c r="D24" t="n">
-        <v>16.22726</v>
+        <v>16.54979</v>
       </c>
       <c r="E24" t="n">
-        <v>16.13059</v>
+        <v>16.5666</v>
       </c>
       <c r="F24" t="n">
-        <v>265.0952</v>
+        <v>264.0358</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.47891</v>
+        <v>16.4892</v>
       </c>
       <c r="D25" t="n">
-        <v>16.38483</v>
+        <v>16.19819</v>
       </c>
       <c r="E25" t="n">
-        <v>16.31215</v>
+        <v>16.41204</v>
       </c>
       <c r="F25" t="n">
-        <v>272.22653</v>
+        <v>261.95409</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.13518</v>
+        <v>16.54894</v>
       </c>
       <c r="D26" t="n">
-        <v>16.45359</v>
+        <v>16.1556</v>
       </c>
       <c r="E26" t="n">
-        <v>16.3724</v>
+        <v>16.23948</v>
       </c>
       <c r="F26" t="n">
-        <v>265.4366</v>
+        <v>260.4971</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.29375</v>
+        <v>16.69944</v>
       </c>
       <c r="D27" t="n">
-        <v>16.09426</v>
+        <v>16.32427</v>
       </c>
       <c r="E27" t="n">
-        <v>16.52494</v>
+        <v>16.40216</v>
       </c>
       <c r="F27" t="n">
-        <v>269.73558</v>
+        <v>267.90237</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.50156</v>
+        <v>16.43536</v>
       </c>
       <c r="D28" t="n">
-        <v>16.46151</v>
+        <v>15.87049</v>
       </c>
       <c r="E28" t="n">
-        <v>16.33002</v>
+        <v>16.0598</v>
       </c>
       <c r="F28" t="n">
-        <v>261.79819</v>
+        <v>263.1659</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.29062</v>
+        <v>16.30635</v>
       </c>
       <c r="D29" t="n">
-        <v>16.49213</v>
+        <v>16.25585</v>
       </c>
       <c r="E29" t="n">
-        <v>16.49859</v>
+        <v>16.30255</v>
       </c>
       <c r="F29" t="n">
-        <v>271.45026</v>
+        <v>266.05407</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.56824</v>
+        <v>16.57123</v>
       </c>
       <c r="D30" t="n">
-        <v>16.21373</v>
+        <v>16.04826</v>
       </c>
       <c r="E30" t="n">
-        <v>16.1695</v>
+        <v>16.24336</v>
       </c>
       <c r="F30" t="n">
-        <v>268.66835</v>
+        <v>271.9485</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.73972</v>
+        <v>17.70078</v>
       </c>
       <c r="D32" t="n">
-        <v>16.58081</v>
+        <v>16.93405</v>
       </c>
       <c r="E32" t="n">
-        <v>17.15171</v>
+        <v>17.41161</v>
       </c>
       <c r="F32" t="n">
-        <v>22.63955</v>
+        <v>23.26122</v>
       </c>
       <c r="G32" t="n">
-        <v>36.56899</v>
+        <v>35.90151</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.71601</v>
+        <v>17.45566</v>
       </c>
       <c r="D33" t="n">
-        <v>16.63786</v>
+        <v>16.85223</v>
       </c>
       <c r="E33" t="n">
-        <v>17.41161</v>
+        <v>17.00108</v>
       </c>
       <c r="F33" t="n">
-        <v>22.44615</v>
+        <v>22.63486</v>
       </c>
       <c r="G33" t="n">
-        <v>36.1374</v>
+        <v>36.16898</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.37375</v>
+        <v>17.4246</v>
       </c>
       <c r="D34" t="n">
-        <v>16.42321</v>
+        <v>16.77084</v>
       </c>
       <c r="E34" t="n">
-        <v>16.83286</v>
+        <v>17.22575</v>
       </c>
       <c r="F34" t="n">
-        <v>22.83102</v>
+        <v>22.41898</v>
       </c>
       <c r="G34" t="n">
-        <v>35.28177</v>
+        <v>36.20334</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.38887</v>
+        <v>17.40515</v>
       </c>
       <c r="D35" t="n">
-        <v>16.94836</v>
+        <v>16.80469</v>
       </c>
       <c r="E35" t="n">
-        <v>16.99653</v>
+        <v>17.40399</v>
       </c>
       <c r="F35" t="n">
-        <v>22.75628</v>
+        <v>22.6281</v>
       </c>
       <c r="G35" t="n">
-        <v>36.07445</v>
+        <v>36.21573</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17.35361</v>
+        <v>17.65271</v>
       </c>
       <c r="D36" t="n">
-        <v>16.99008</v>
+        <v>16.62643</v>
       </c>
       <c r="E36" t="n">
-        <v>17.19969</v>
+        <v>16.76392</v>
       </c>
       <c r="F36" t="n">
-        <v>22.92301</v>
+        <v>22.88148</v>
       </c>
       <c r="G36" t="n">
-        <v>35.79236</v>
+        <v>36.00515</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18.04816</v>
+        <v>17.45436</v>
       </c>
       <c r="D37" t="n">
-        <v>16.67287</v>
+        <v>17.05814</v>
       </c>
       <c r="E37" t="n">
-        <v>17.04386</v>
+        <v>17.11423</v>
       </c>
       <c r="F37" t="n">
-        <v>23.0321</v>
+        <v>22.34988</v>
       </c>
       <c r="G37" t="n">
-        <v>36.13048</v>
+        <v>35.76053</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17.2735</v>
+        <v>17.56275</v>
       </c>
       <c r="D38" t="n">
-        <v>16.63698</v>
+        <v>16.72375</v>
       </c>
       <c r="E38" t="n">
-        <v>17.01718</v>
+        <v>16.90198</v>
       </c>
       <c r="F38" t="n">
-        <v>22.28297</v>
+        <v>23.12106</v>
       </c>
       <c r="G38" t="n">
-        <v>35.82776</v>
+        <v>36.74284</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.64089</v>
+        <v>17.78008</v>
       </c>
       <c r="D39" t="n">
-        <v>16.64408</v>
+        <v>16.60099</v>
       </c>
       <c r="E39" t="n">
-        <v>17.14682</v>
+        <v>17.3951</v>
       </c>
       <c r="F39" t="n">
-        <v>22.89728</v>
+        <v>22.50847</v>
       </c>
       <c r="G39" t="n">
-        <v>36.23044</v>
+        <v>36.03521</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.41061</v>
+        <v>17.51378</v>
       </c>
       <c r="D40" t="n">
-        <v>16.31587</v>
+        <v>17.00495</v>
       </c>
       <c r="E40" t="n">
-        <v>17.15414</v>
+        <v>17.25805</v>
       </c>
       <c r="F40" t="n">
-        <v>22.77466</v>
+        <v>22.41821</v>
       </c>
       <c r="G40" t="n">
-        <v>36.57314</v>
+        <v>35.21452</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.39718</v>
+        <v>17.89094</v>
       </c>
       <c r="D42" t="n">
-        <v>16.98553</v>
+        <v>16.64767</v>
       </c>
       <c r="E42" t="n">
-        <v>17.08382</v>
+        <v>17.23972</v>
       </c>
       <c r="F42" t="n">
-        <v>22.60805</v>
+        <v>23.22072</v>
       </c>
       <c r="G42" t="n">
-        <v>35.57549</v>
+        <v>35.80556</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17.89342</v>
+        <v>17.77844</v>
       </c>
       <c r="D43" t="n">
-        <v>16.88844</v>
+        <v>16.60263</v>
       </c>
       <c r="E43" t="n">
-        <v>16.99289</v>
+        <v>17.15556</v>
       </c>
       <c r="F43" t="n">
-        <v>23.0386</v>
+        <v>22.55568</v>
       </c>
       <c r="G43" t="n">
-        <v>35.70624</v>
+        <v>36.45171</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17.73777</v>
+        <v>17.32161</v>
       </c>
       <c r="D44" t="n">
-        <v>16.79416</v>
+        <v>16.43533</v>
       </c>
       <c r="E44" t="n">
-        <v>17.13306</v>
+        <v>17.31023</v>
       </c>
       <c r="F44" t="n">
-        <v>23.05196</v>
+        <v>22.7272</v>
       </c>
       <c r="G44" t="n">
-        <v>35.59274</v>
+        <v>35.61495</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17.23376</v>
+        <v>17.58763</v>
       </c>
       <c r="D45" t="n">
-        <v>16.78581</v>
+        <v>16.93949</v>
       </c>
       <c r="E45" t="n">
-        <v>17.19085</v>
+        <v>17.23157</v>
       </c>
       <c r="F45" t="n">
-        <v>22.6349</v>
+        <v>22.80856</v>
       </c>
       <c r="G45" t="n">
-        <v>35.85992</v>
+        <v>36.16947</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>17.50565</v>
+        <v>17.33416</v>
       </c>
       <c r="D46" t="n">
-        <v>16.41217</v>
+        <v>16.62728</v>
       </c>
       <c r="E46" t="n">
-        <v>17.24272</v>
+        <v>17.07481</v>
       </c>
       <c r="F46" t="n">
-        <v>22.92409</v>
+        <v>22.56807</v>
       </c>
       <c r="G46" t="n">
-        <v>36.07165</v>
+        <v>36.21687</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.73822</v>
+        <v>17.47115</v>
       </c>
       <c r="D47" t="n">
-        <v>16.87994</v>
+        <v>16.85422</v>
       </c>
       <c r="E47" t="n">
-        <v>17.34324</v>
+        <v>17.35287</v>
       </c>
       <c r="F47" t="n">
-        <v>22.72715</v>
+        <v>22.6091</v>
       </c>
       <c r="G47" t="n">
-        <v>35.72308</v>
+        <v>35.63548</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17.50393</v>
+        <v>17.54533</v>
       </c>
       <c r="D48" t="n">
-        <v>16.75499</v>
+        <v>16.97474</v>
       </c>
       <c r="E48" t="n">
-        <v>17.11686</v>
+        <v>16.98894</v>
       </c>
       <c r="F48" t="n">
-        <v>22.69532</v>
+        <v>22.86624</v>
       </c>
       <c r="G48" t="n">
-        <v>35.80886</v>
+        <v>37.00055</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17.68161</v>
+        <v>17.73631</v>
       </c>
       <c r="D49" t="n">
-        <v>16.77864</v>
+        <v>16.77523</v>
       </c>
       <c r="E49" t="n">
-        <v>17.02636</v>
+        <v>17.09928</v>
       </c>
       <c r="F49" t="n">
-        <v>22.55444</v>
+        <v>22.79728</v>
       </c>
       <c r="G49" t="n">
-        <v>35.06066</v>
+        <v>35.30024</v>
       </c>
     </row>
     <row r="50">
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17.46237</v>
+        <v>17.53241</v>
       </c>
       <c r="D50" t="n">
-        <v>16.86076</v>
+        <v>16.78682</v>
       </c>
       <c r="E50" t="n">
-        <v>17.34915</v>
+        <v>17.00801</v>
       </c>
       <c r="F50" t="n">
-        <v>22.95473</v>
+        <v>22.83463</v>
       </c>
       <c r="G50" t="n">
-        <v>35.76608</v>
+        <v>36.30379</v>
       </c>
     </row>
     <row r="51">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.64347</v>
+        <v>0.64717</v>
       </c>
       <c r="D52" t="n">
-        <v>1.16255</v>
+        <v>1.18651</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.64718</v>
+        <v>0.63491</v>
       </c>
       <c r="D53" t="n">
-        <v>1.16067</v>
+        <v>1.15978</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.63497</v>
+        <v>0.63398</v>
       </c>
       <c r="D54" t="n">
-        <v>1.17685</v>
+        <v>1.16691</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.6323299999999999</v>
+        <v>0.63337</v>
       </c>
       <c r="D55" t="n">
-        <v>1.19451</v>
+        <v>1.16687</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.62925</v>
+        <v>0.63087</v>
       </c>
       <c r="D56" t="n">
-        <v>1.17211</v>
+        <v>1.16408</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.64113</v>
+        <v>0.64415</v>
       </c>
       <c r="D57" t="n">
-        <v>1.14993</v>
+        <v>1.14512</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.62729</v>
+        <v>0.60765</v>
       </c>
       <c r="D58" t="n">
-        <v>1.14834</v>
+        <v>1.16056</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.63315</v>
+        <v>0.63694</v>
       </c>
       <c r="D59" t="n">
-        <v>1.15209</v>
+        <v>1.17986</v>
       </c>
     </row>
     <row r="60">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.63093</v>
+        <v>0.6233</v>
       </c>
       <c r="D60" t="n">
-        <v>1.16318</v>
+        <v>1.15595</v>
       </c>
     </row>
     <row r="61">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.64111</v>
+        <v>0.65071</v>
       </c>
       <c r="D62" t="n">
-        <v>1.15956</v>
+        <v>1.18079</v>
       </c>
     </row>
     <row r="63">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.63913</v>
+        <v>0.63666</v>
       </c>
       <c r="D63" t="n">
-        <v>1.17037</v>
+        <v>1.17309</v>
       </c>
     </row>
     <row r="64">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.63401</v>
+        <v>0.64636</v>
       </c>
       <c r="D64" t="n">
-        <v>1.15956</v>
+        <v>1.16369</v>
       </c>
     </row>
     <row r="65">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.63443</v>
+        <v>0.64279</v>
       </c>
       <c r="D65" t="n">
-        <v>1.16976</v>
+        <v>1.18178</v>
       </c>
     </row>
     <row r="66">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.63872</v>
+        <v>0.62787</v>
       </c>
       <c r="D66" t="n">
-        <v>1.15746</v>
+        <v>1.15496</v>
       </c>
     </row>
     <row r="67">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.63276</v>
+        <v>0.64656</v>
       </c>
       <c r="D67" t="n">
-        <v>1.18934</v>
+        <v>1.17367</v>
       </c>
     </row>
     <row r="68">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.64427</v>
+        <v>0.6422600000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>1.16683</v>
+        <v>1.15196</v>
       </c>
     </row>
     <row r="69">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.63532</v>
+        <v>0.64023</v>
       </c>
       <c r="D69" t="n">
-        <v>1.181</v>
+        <v>1.17281</v>
       </c>
     </row>
     <row r="70">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.63098</v>
+        <v>0.64049</v>
       </c>
       <c r="D70" t="n">
-        <v>1.15708</v>
+        <v>1.17842</v>
       </c>
     </row>
   </sheetData>
